--- a/data/trans_orig/IP33A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP33A-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>38,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12425</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12418</t>
+          <t>12196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>14052</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>16679</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24393</t>
+          <t>24302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1233</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>10332</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>66,25%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>74,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>11014</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>65,32%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>9682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>16795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,03%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,38%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12158</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,33%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11364</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>14943</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,99%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18816</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>6804</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14200</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15754</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25508</t>
+          <t>25270</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9479</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16979</t>
+          <t>16971</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11905</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18585</t>
+          <t>18653</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14987</t>
+          <t>15538</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>23259</t>
+          <t>23267</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32503</t>
+          <t>32601</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38629</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>31453</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47646</t>
+          <t>48135</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>58841</t>
+          <t>59035</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>80769</t>
+          <t>81311</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,86%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>60871</t>
+          <t>60771</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>76322</t>
+          <t>75585</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51930</t>
+          <t>51441</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>68123</t>
+          <t>67436</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>118208</t>
+          <t>117666</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>140136</t>
+          <t>139942</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,33%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22375</t>
+          <t>22298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>14641</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,38%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>17017</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12439</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18655</t>
+          <t>18313</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27842</t>
+          <t>27618</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7387</t>
+          <t>7548</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10989</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>59,72%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>8267</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7879</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15413</t>
+          <t>15127</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16278</t>
+          <t>16548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>56,07%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11064</t>
+          <t>10891</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12740</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>12965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22289</t>
+          <t>21895</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>74,19%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>58,5%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13997</t>
+          <t>14378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>80,8%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>909</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>701</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,85%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>798</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8636</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12527</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,4%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>19559</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>15361</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31865</t>
+          <t>32470</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>23468</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18872</t>
+          <t>19692</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27713</t>
+          <t>27108</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40452</t>
+          <t>39400</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>66,13%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9811</t>
+          <t>9608</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21435</t>
+          <t>21512</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>18497</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26714</t>
+          <t>26452</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20136</t>
+          <t>20339</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27124</t>
+          <t>27130</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>40912</t>
+          <t>40835</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>51893</t>
+          <t>51701</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49611</t>
+          <t>49952</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>69116</t>
+          <t>68870</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>34716</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52600</t>
+          <t>52840</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>89649</t>
+          <t>90814</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>115651</t>
+          <t>116654</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>66820</t>
+          <t>67066</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>86325</t>
+          <t>85984</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>79192</t>
+          <t>78952</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>96327</t>
+          <t>97076</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>152077</t>
+          <t>151074</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>178079</t>
+          <t>176914</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14183</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10776</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13745</t>
+          <t>13683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>23146</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>65,37%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12813</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>21725</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,36%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>12243</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18475</t>
+          <t>18554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>21772</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28384</t>
+          <t>28339</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34820</t>
+          <t>34741</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45018</t>
+          <t>45064</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>11254</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>7691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>49,01%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15335</t>
+          <t>14787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18739</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28506</t>
+          <t>27716</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>78,28%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19002</t>
+          <t>19119</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11179</t>
+          <t>12146</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19970</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26030</t>
+          <t>25825</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37223</t>
+          <t>37135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,4%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13485</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14755</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>13460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24565</t>
+          <t>24770</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,96%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17486</t>
+          <t>17494</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20095</t>
+          <t>20404</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>14453</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25609</t>
+          <t>25254</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27271</t>
+          <t>26860</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42599</t>
+          <t>42797</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,37%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33034</t>
+          <t>32725</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>43036</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24701</t>
+          <t>25056</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35915</t>
+          <t>35857</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60840</t>
+          <t>60642</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>76168</t>
+          <t>76579</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>74,03%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>14448</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23717</t>
+          <t>24175</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18733</t>
+          <t>18985</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26422</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39725</t>
+          <t>39735</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,56%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>13263</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23674</t>
+          <t>22990</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>15089</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24915</t>
+          <t>24402</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31787</t>
+          <t>31777</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45203</t>
+          <t>45090</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>65540</t>
+          <t>65082</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>85500</t>
+          <t>86400</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>60337</t>
+          <t>59990</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>82929</t>
+          <t>82457</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>132187</t>
+          <t>132385</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>163245</t>
+          <t>161853</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>101979</t>
+          <t>101079</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>121939</t>
+          <t>122397</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>109567</t>
+          <t>110039</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>132159</t>
+          <t>132506</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>216730</t>
+          <t>218122</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>247788</t>
+          <t>247590</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,16%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13265</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19245</t>
+          <t>19464</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13326</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12381</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>14185</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24000</t>
+          <t>23889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,0%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16158</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11340</t>
+          <t>11367</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21770</t>
+          <t>22810</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21235</t>
+          <t>21595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35078</t>
+          <t>35070</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,71%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17291</t>
+          <t>17057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18567</t>
+          <t>17527</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28997</t>
+          <t>28970</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29027</t>
+          <t>29035</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42870</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,31%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13768</t>
+          <t>13465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7075</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>12946</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>16623</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25314</t>
+          <t>25229</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12175</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9578</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24345</t>
+          <t>24704</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17892</t>
+          <t>18166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36026</t>
+          <t>35647</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>10804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>16038</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>56,7%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>960</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>58,11%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>738</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11790</t>
+          <t>11967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>699</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7892</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>72,94%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19377</t>
+          <t>19580</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9279</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26252</t>
+          <t>26594</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20113</t>
+          <t>20177</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,84%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21261</t>
+          <t>20656</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24556</t>
+          <t>24214</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41529</t>
+          <t>41739</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60924</t>
+          <t>60860</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23880</t>
+          <t>23611</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26146</t>
+          <t>26916</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33211</t>
+          <t>33301</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52969</t>
+          <t>52278</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>60118</t>
+          <t>60008</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>40872</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>60982</t>
+          <t>60145</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>60388</t>
+          <t>60070</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>98421</t>
+          <t>97439</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>108098</t>
+          <t>105823</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>150496</t>
+          <t>148957</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>82176</t>
+          <t>83013</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>102286</t>
+          <t>102045</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>98105</t>
+          <t>99087</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>136138</t>
+          <t>136456</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>189188</t>
+          <t>190727</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>231586</t>
+          <t>233861</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>
